--- a/v3/outputs/FINAL_Xenium_panel_ORBm_BMAp_for_MSGS111.xlsx
+++ b/v3/outputs/FINAL_Xenium_panel_ORBm_BMAp_for_MSGS111.xlsx
@@ -461,8 +461,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="49" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
@@ -537,6 +537,18 @@
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Col23a1, Slc29a4, Cck, Gfra1, Sp8, Abca8a, Calcrl, Lamb3, Syndig1l, Tspan18, Gabre, Nos1, Oprl1, Dnah5 were added at the bottom of SHARED_PANEL_ORDER and BMAp_ORDER. No existing gene was removed or re-ranked. These 14 extra custom slots are on top of the original 100.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>10 genes appended (Jesse ORB: morphine state + GPCR map, including optional Camk2g / Gpr26)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Block 13_Jesse_morphine_state: Per2, Pcsk1, Per1, Camk2g, Bhlhe40, Sema3e. Block 14_Jesse_ORB_GPCR: Chrm1, Grm8, Gpr26, Rxfp1. 7 new custom slots (Per2, Pcsk1, Per1, Camk2g, Chrm1, Grm8, Gpr26); Bhlhe40, Sema3e, Rxfp1 are already free on the 10x Mouse Brain v1 base panel (0 slots). Added at the bottom of SHARED_PANEL_ORDER and ORBm_ORDER. Per1 was already on ORBm_ORDER as a circadian IEG and is now also on the shared order list (not duplicated on ORBm_ORDER). No existing gene was removed or re-ranked. BMAp_ORDER is unchanged because Jesse's data is PL-ILA-ORB. Shared panel is now 168 genes = 47 free on base + 121 custom (was 158 = 44 + 114). These genes report morphine-dependence state or the ORB GPCR map, not cell type, so ANCHOR_COVERAGE is unchanged and all 20 cell types remain separable. Not added: Mas1, Gpr68, Mchr1, Arid5b, Gadd45a, Sfrp1, Glipr1, Vdr, or the rest of Jesse's 304 DEGs.</t>
         </is>
       </c>
     </row>
@@ -551,8 +563,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H159"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:H169"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
@@ -5940,6 +5952,286 @@
         <v>0.53</v>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Per2</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>13_Jesse_morphine_state</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>morphine-dependence state :: 11/12 ORBm anchors Up</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Added from Jesse Niehaus PL-ILA-ORB opioid-dependence DEGs (5-day escalating morphine, DESeq2 subclass pseudobulk, padj&lt;=0.1). Ranked by how many of the 12 ORBm anchor subclasses show DE. Reports morphine-dependence state, NOT cell type. No existing gene was removed or re-ranked. || Broadest gene in Jesse's data: 11 of 12 ORBm anchors, glut 8 / GABA 3. Circadian clock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Pcsk1</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>13_Jesse_morphine_state</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>morphine-dependence state :: 9/12 ORBm anchors Up</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Added from Jesse Niehaus PL-ILA-ORB opioid-dependence DEGs (5-day escalating morphine, DESeq2 subclass pseudobulk, padj&lt;=0.1). Ranked by how many of the 12 ORBm anchor subclasses show DE. Reports morphine-dependence state, NOT cell type. No existing gene was removed or re-ranked. || 9 of 12 anchors. Prohormone convertase 1 (proenkephalin / POMC processing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Per1</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>13_Jesse_morphine_state</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>morphine-dependence state :: 8/12 ORBm anchors Up</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Added from Jesse Niehaus PL-ILA-ORB opioid-dependence DEGs (5-day escalating morphine, DESeq2 subclass pseudobulk, padj&lt;=0.1). Ranked by how many of the 12 ORBm anchor subclasses show DE. Reports morphine-dependence state, NOT cell type. No existing gene was removed or re-ranked. || 8 of 12 anchors. Second clock gene; confirms Per2. Already listed on ORBm_ORDER as a circadian IEG; added here so it is on the shared order list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Camk2g</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>13_Jesse_morphine_state</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>morphine-dependence state :: 6/12 ORBm anchors Down</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Added from Jesse Niehaus PL-ILA-ORB opioid-dependence DEGs (5-day escalating morphine, DESeq2 subclass pseudobulk, padj&lt;=0.1). Ranked by how many of the 12 ORBm anchor subclasses show DE. Reports morphine-dependence state, NOT cell type. No existing gene was removed or re-ranked. || Strongest Down gene (glut only). Direction control. Allen ORBm max 93% (L6 CT).</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="G163" t="n">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Bhlhe40</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>13_Jesse_morphine_state</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>morphine-dependence state :: 4/12 ORBm anchors Up</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Added from Jesse Niehaus PL-ILA-ORB opioid-dependence DEGs (5-day escalating morphine, DESeq2 subclass pseudobulk, padj&lt;=0.1). Ranked by how many of the 12 ORBm anchor subclasses show DE. Reports morphine-dependence state, NOT cell type. No existing gene was removed or re-ranked. || Metabolic / circadian TF. Free on the Xenium Mouse Brain v1 base panel (0 slots).</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Sema3e</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>13_Jesse_morphine_state</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>morphine-dependence state :: 3/12 ORBm anchors Up</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Added from Jesse Niehaus PL-ILA-ORB opioid-dependence DEGs (5-day escalating morphine, DESeq2 subclass pseudobulk, padj&lt;=0.1). Ranked by how many of the 12 ORBm anchor subclasses show DE. Reports morphine-dependence state, NOT cell type. No existing gene was removed or re-ranked. || Free on the Xenium Mouse Brain v1 base panel (0 slots).</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Chrm1</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>14_Jesse_ORB_GPCR</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>ORB-enriched GPCR :: Chrm1 92% Allen ORBm (L2/3 IT)</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Added from Jesse Niehaus PL-ILA-ORB enriched-GPCR list (vs the rest of the Allen 4M-cell atlas), then filtered by Allen ORBm absolute % expressing (106,122 cells). Serves the druggable receptor map. No existing gene was removed or re-ranked. || M1 muscarinic (Gq). Allen 92%, 9/12 anchors &gt;=50%. Panel already has Chrm2 (M2, Gi) — opposite signalling.</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>92</v>
+      </c>
+      <c r="G166" t="n">
+        <v>6.68</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Grm8</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>14_Jesse_ORB_GPCR</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>ORB-enriched GPCR :: Grm8 99% Allen ORBm (L5 ET)</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Added from Jesse Niehaus PL-ILA-ORB enriched-GPCR list (vs the rest of the Allen 4M-cell atlas), then filtered by Allen ORBm absolute % expressing (106,122 cells). Serves the druggable receptor map. No existing gene was removed or re-ranked. || mGlu8, group III (Gi). Allen 99%, 8/12 anchors &gt;=50%. Panel has Grm1/Grm5 (group I, Gq) only.</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="G167" t="n">
+        <v>8.66</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Gpr26</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>14_Jesse_ORB_GPCR</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>ORB-enriched GPCR :: Gpr26 86% Allen ORBm (L4/5 IT)</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Added from Jesse Niehaus PL-ILA-ORB enriched-GPCR list (vs the rest of the Allen 4M-cell atlas), then filtered by Allen ORBm absolute % expressing (106,122 cells). Serves the druggable receptor map. No existing gene was removed or re-ranked. || Optional high-abundance ORB GPCR. Allen 86%, 7/12 anchors &gt;=50%. Broader than Chrm1/Cckbr; kept because it is actually visible.</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="G168" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Rxfp1</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>14_Jesse_ORB_GPCR</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>ORB-enriched GPCR :: Rxfp1 free on base, Allen 34% (L5 ET)</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Added from Jesse Niehaus PL-ILA-ORB enriched-GPCR list (vs the rest of the Allen 4M-cell atlas), then filtered by Allen ORBm absolute % expressing (106,122 cells). Serves the druggable receptor map. No existing gene was removed or re-ranked. || Jesse's #2 ORB-enriched GPCR. Free on the Xenium Mouse Brain v1 base panel (0 slots). Circuit-proximity marker, not a morphine DEG.</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="G169" t="n">
+        <v>2.32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5951,8 +6243,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E141"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:E150"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
@@ -9484,6 +9776,231 @@
       <c r="E141" t="inlineStr">
         <is>
           <t>DAT. Definitive dopaminergic; expected near-absent in ORBm/BMAp so it acts as a negative control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Per2</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>13_Jesse_morphine_state</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>morphine-dependence state :: 11/12 ORBm anchors Up</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Added from Jesse Niehaus PL-ILA-ORB opioid-dependence DEGs (5-day escalating morphine, DESeq2 subclass pseudobulk, padj&lt;=0.1). Ranked by how many of the 12 ORBm anchor subclasses show DE. Reports morphine-dependence state, NOT cell type. No existing gene was removed or re-ranked. || Broadest gene in Jesse's data: 11 of 12 ORBm anchors, glut 8 / GABA 3. Circadian clock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Pcsk1</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>13_Jesse_morphine_state</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>morphine-dependence state :: 9/12 ORBm anchors Up</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Added from Jesse Niehaus PL-ILA-ORB opioid-dependence DEGs (5-day escalating morphine, DESeq2 subclass pseudobulk, padj&lt;=0.1). Ranked by how many of the 12 ORBm anchor subclasses show DE. Reports morphine-dependence state, NOT cell type. No existing gene was removed or re-ranked. || 9 of 12 anchors. Prohormone convertase 1 (proenkephalin / POMC processing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Camk2g</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>13_Jesse_morphine_state</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>morphine-dependence state :: 6/12 ORBm anchors Down</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Added from Jesse Niehaus PL-ILA-ORB opioid-dependence DEGs (5-day escalating morphine, DESeq2 subclass pseudobulk, padj&lt;=0.1). Ranked by how many of the 12 ORBm anchor subclasses show DE. Reports morphine-dependence state, NOT cell type. No existing gene was removed or re-ranked. || Strongest Down gene (glut only). Direction control. Allen ORBm max 93% (L6 CT).</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Bhlhe40</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>13_Jesse_morphine_state</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>morphine-dependence state :: 4/12 ORBm anchors Up</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Added from Jesse Niehaus PL-ILA-ORB opioid-dependence DEGs (5-day escalating morphine, DESeq2 subclass pseudobulk, padj&lt;=0.1). Ranked by how many of the 12 ORBm anchor subclasses show DE. Reports morphine-dependence state, NOT cell type. No existing gene was removed or re-ranked. || Metabolic / circadian TF. Free on the Xenium Mouse Brain v1 base panel (0 slots).</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Sema3e</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>13_Jesse_morphine_state</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>morphine-dependence state :: 3/12 ORBm anchors Up</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Added from Jesse Niehaus PL-ILA-ORB opioid-dependence DEGs (5-day escalating morphine, DESeq2 subclass pseudobulk, padj&lt;=0.1). Ranked by how many of the 12 ORBm anchor subclasses show DE. Reports morphine-dependence state, NOT cell type. No existing gene was removed or re-ranked. || Free on the Xenium Mouse Brain v1 base panel (0 slots).</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Chrm1</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>14_Jesse_ORB_GPCR</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ORB-enriched GPCR :: Chrm1 92% Allen ORBm (L2/3 IT)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Added from Jesse Niehaus PL-ILA-ORB enriched-GPCR list (vs the rest of the Allen 4M-cell atlas), then filtered by Allen ORBm absolute % expressing (106,122 cells). Serves the druggable receptor map. No existing gene was removed or re-ranked. || M1 muscarinic (Gq). Allen 92%, 9/12 anchors &gt;=50%. Panel already has Chrm2 (M2, Gi) — opposite signalling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Grm8</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>14_Jesse_ORB_GPCR</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ORB-enriched GPCR :: Grm8 99% Allen ORBm (L5 ET)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Added from Jesse Niehaus PL-ILA-ORB enriched-GPCR list (vs the rest of the Allen 4M-cell atlas), then filtered by Allen ORBm absolute % expressing (106,122 cells). Serves the druggable receptor map. No existing gene was removed or re-ranked. || mGlu8, group III (Gi). Allen 99%, 8/12 anchors &gt;=50%. Panel has Grm1/Grm5 (group I, Gq) only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Gpr26</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>14_Jesse_ORB_GPCR</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>ORB-enriched GPCR :: Gpr26 86% Allen ORBm (L4/5 IT)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Added from Jesse Niehaus PL-ILA-ORB enriched-GPCR list (vs the rest of the Allen 4M-cell atlas), then filtered by Allen ORBm absolute % expressing (106,122 cells). Serves the druggable receptor map. No existing gene was removed or re-ranked. || Optional high-abundance ORB GPCR. Allen 86%, 7/12 anchors &gt;=50%. Broader than Chrm1/Cckbr; kept because it is actually visible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Rxfp1</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>14_Jesse_ORB_GPCR</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>ORB-enriched GPCR :: Rxfp1 free on base, Allen 34% (L5 ET)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Added from Jesse Niehaus PL-ILA-ORB enriched-GPCR list (vs the rest of the Allen 4M-cell atlas), then filtered by Allen ORBm absolute % expressing (106,122 cells). Serves the druggable receptor map. No existing gene was removed or re-ranked. || Jesse's #2 ORB-enriched GPCR. Free on the Xenium Mouse Brain v1 base panel (0 slots). Circuit-proximity marker, not a morphine DEG.</t>
         </is>
       </c>
     </row>
@@ -9499,7 +10016,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E141"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
@@ -13046,7 +13563,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
@@ -13699,8 +14216,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:K14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -14335,6 +14852,91 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Niehaus2026_ORB</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Jesse Niehaus (personal communication)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Niehaus J. PL-ILA-ORB opioid-dependence DEGs and enriched GPCRs, shared 2026-09-09.</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>unpublished</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Opioid-dependence DEGs (IEG 77, TF 179, synaptic plasticity 45, GPCR 34) from 5-day escalating morphine, DESeq2 subclass pseudobulk padj&lt;=0.1, plus PL-ILA-ORB enriched GPCRs. Basis for blocks 13_Jesse_morphine_state and 14_Jesse_ORB_GPCR. Replaces the Lui2021 stand-in for Jesse's ORBm list.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Received as per-subclass DEG tables (gene, n_DE_clusters, direction, DE_clusters), not raw counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GSE283418</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Berg &amp; Scherrer (GSE283418)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Spatial molecular profiling of amygdalar neurons enables precision pharmacology against pain unpleasantness.</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>GEO dataset</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/geo/query/acc.cgi?acc=GSE283418</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Custom 98-gene Resolve Molecular Cartography amygdala panel. 14 genes scored as BMAp-informative in Allen were appended as block 12_GSE283418_added. Remaining off-panel genes (including Sfrp1, Glipr1, Vdr) all score max_spec &lt; 1.0, so nothing further was added. Replaces the Hochgerner2023 stand-in.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>GEO metadata only (family.soft, series matrix); no raw expression matrix downloaded.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
